--- a/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,88</t>
+          <t>0,55; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,61</t>
+          <t>0,71; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,82</t>
+          <t>0,18; 1,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,38</t>
+          <t>1,13; 3,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,09</t>
+          <t>0,95; 4,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,31</t>
+          <t>1,36; 5,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,39</t>
+          <t>1,22; 3,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,74</t>
+          <t>0,9; 2,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,03</t>
+          <t>1,37; 3,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,08</t>
+          <t>0,12; 1,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,94</t>
+          <t>1,37; 3,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,64</t>
+          <t>0,78; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,92</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,39</t>
+          <t>0,25; 2,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,9</t>
+          <t>1,53; 4,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,54</t>
+          <t>0,25; 2,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,41</t>
+          <t>0,32; 3,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,24</t>
+          <t>0,54; 3,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,05</t>
+          <t>1,19; 3,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,4</t>
+          <t>0,68; 2,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,87</t>
+          <t>0,39; 1,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,14</t>
+          <t>0,55; 2,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,87</t>
+          <t>1,59; 3,86</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,32</t>
+          <t>1,0; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,65</t>
+          <t>0,4; 2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,75</t>
+          <t>0,54; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,54</t>
+          <t>0,57; 5,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,66</t>
+          <t>1,1; 5,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,94</t>
+          <t>1,88; 10,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,2</t>
+          <t>0,45; 2,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,36</t>
+          <t>1,28; 3,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,65</t>
+          <t>0,45; 2,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,27</t>
+          <t>0,89; 4,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,6</t>
+          <t>1,12; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,06</t>
+          <t>1,25; 2,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,81</t>
+          <t>0,54; 2,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,36</t>
+          <t>1,52; 3,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,56</t>
+          <t>0,73; 2,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,06</t>
+          <t>1,48; 3,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,13</t>
+          <t>0,58; 2,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 60,38</t>
+          <t>1,94; 52,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,24</t>
+          <t>1,19; 2,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,0</t>
+          <t>1,48; 2,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,64</t>
+          <t>0,63; 1,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 37,63</t>
+          <t>2,06; 40,7</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,6</t>
+          <t>1,08; 4,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,25</t>
+          <t>0,4; 2,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,84</t>
+          <t>0,73; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,26</t>
+          <t>1,67; 5,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,45</t>
+          <t>0,56; 2,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,24</t>
+          <t>1,08; 3,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,28</t>
+          <t>0,62; 2,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,37</t>
+          <t>2,78; 5,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,67</t>
+          <t>0,94; 2,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,51</t>
+          <t>0,95; 2,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,2</t>
+          <t>0,8; 2,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,72</t>
+          <t>2,84; 4,77</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,01</t>
+          <t>0,72; 5,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,75</t>
+          <t>0,12; 2,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,98</t>
+          <t>1,3; 2,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,12</t>
+          <t>1,37; 3,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,82</t>
+          <t>0,45; 1,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,18</t>
+          <t>2,27; 4,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,2; 2,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,93</t>
+          <t>1,36; 2,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,53</t>
+          <t>0,45; 1,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,43</t>
+          <t>1,86; 3,4</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,1</t>
+          <t>1,15; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,15</t>
+          <t>1,28; 2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,44</t>
+          <t>0,68; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,85</t>
+          <t>1,68; 2,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,16</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,67</t>
+          <t>1,69; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,45</t>
+          <t>0,75; 1,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 25,45</t>
+          <t>2,82; 25,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,91</t>
+          <t>1,31; 1,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,25</t>
+          <t>1,62; 2,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,97</t>
+          <t>2,47; 15,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2480; 13643</t>
+          <t>2612; 13836</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2930; 15805</t>
+          <t>3099; 16413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>783; 7817</t>
+          <t>782; 7050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4874; 17101</t>
+          <t>5728; 18517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2882; 12530</t>
+          <t>2914; 13333</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4424; 19857</t>
+          <t>4283; 18722</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4833</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5412; 15187</t>
+          <t>5468; 15340</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6786; 21368</t>
+          <t>7019; 21690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9845; 30300</t>
+          <t>10266; 29286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>940; 8386</t>
+          <t>895; 8045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12528; 28018</t>
+          <t>13013; 28729</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2975; 13342</t>
+          <t>2860; 13180</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>859; 8053</t>
+          <t>771; 7380</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>964; 9004</t>
+          <t>949; 8354</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6533; 22153</t>
+          <t>6899; 22220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>926; 9463</t>
+          <t>915; 8149</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1881; 11540</t>
+          <t>1096; 10413</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2812; 12048</t>
+          <t>2024; 11996</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4297; 15501</t>
+          <t>4558; 14471</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4891; 17766</t>
+          <t>4988; 17641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3134; 14181</t>
+          <t>2946; 13284</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4713; 16070</t>
+          <t>4153; 17064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13767; 32308</t>
+          <t>13248; 32195</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1854; 11055</t>
+          <t>1869; 11039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5998; 20913</t>
+          <t>6316; 23334</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1628; 13840</t>
+          <t>2066; 13077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3078; 25041</t>
+          <t>3641; 26991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>931; 9302</t>
+          <t>951; 8550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2036; 12111</t>
+          <t>2857; 13201</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 10063</t>
+          <t>0; 10417</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3092; 16599</t>
+          <t>3137; 17236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3576; 15599</t>
+          <t>3217; 14624</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11286; 29901</t>
+          <t>11347; 30612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3213; 18230</t>
+          <t>3110; 16560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7472; 35633</t>
+          <t>7432; 35035</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13559; 32157</t>
+          <t>13819; 32976</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14902; 35419</t>
+          <t>14456; 33980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5550; 20827</t>
+          <t>6193; 23478</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15296; 34791</t>
+          <t>15769; 35442</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5050; 18256</t>
+          <t>5229; 18006</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11473; 31132</t>
+          <t>11316; 29463</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4876; 17617</t>
+          <t>4764; 16900</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19122; 590596</t>
+          <t>18952; 518310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21409; 43737</t>
+          <t>23270; 47372</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30564; 57712</t>
+          <t>28486; 56428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12728; 32485</t>
+          <t>12447; 33177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41729; 757435</t>
+          <t>41542; 819284</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3666; 16130</t>
+          <t>3779; 16501</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2043; 11480</t>
+          <t>2062; 11623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4211; 17655</t>
+          <t>4546; 18590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8103; 24995</t>
+          <t>7917; 24612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3228; 13932</t>
+          <t>3165; 14353</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8301; 24676</t>
+          <t>8217; 24243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4685; 16837</t>
+          <t>4607; 16326</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24313; 45145</t>
+          <t>23427; 45280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8600; 24554</t>
+          <t>8656; 24679</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12617; 31914</t>
+          <t>12092; 30520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11122; 29857</t>
+          <t>10848; 28521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37532; 62150</t>
+          <t>37370; 62792</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8394</t>
+          <t>0; 8749</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1057; 13358</t>
+          <t>1924; 13849</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6484</t>
+          <t>0; 5826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157; 4212</t>
+          <t>296; 5023</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16984; 37185</t>
+          <t>16248; 37256</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14311; 34568</t>
+          <t>15238; 35612</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5112; 19655</t>
+          <t>4846; 18710</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17486; 31861</t>
+          <t>17319; 31459</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17737; 39514</t>
+          <t>18574; 40164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18660; 40363</t>
+          <t>18741; 40648</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6396; 20946</t>
+          <t>6119; 21387</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18520; 34318</t>
+          <t>18662; 34062</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>39581; 68772</t>
+          <t>37639; 67095</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42414; 73441</t>
+          <t>43631; 76591</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23487; 48859</t>
+          <t>23001; 48689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55439; 96217</t>
+          <t>56748; 95418</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44180; 73082</t>
+          <t>42920; 74087</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59273; 94783</t>
+          <t>59959; 94752</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26279; 51295</t>
+          <t>26445; 52401</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99391; 910690</t>
+          <t>100983; 929866</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>84652; 126934</t>
+          <t>87079; 130229</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>108943; 156620</t>
+          <t>112766; 159654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56144; 91710</t>
+          <t>55780; 91935</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>172232; 1041230</t>
+          <t>172038; 1079339</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,92</t>
+          <t>0,51; 2,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,75</t>
+          <t>0,69; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,64</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,67</t>
+          <t>1,08; 3,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,35</t>
+          <t>0,91; 4,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,95</t>
+          <t>1,45; 5,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,43</t>
+          <t>1,35; 3,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,78</t>
+          <t>0,9; 2,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,9</t>
+          <t>1,29; 3,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,04</t>
+          <t>0,12; 1,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,38; 2,92</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,59</t>
+          <t>0,77; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,2; 1,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,21</t>
+          <t>0,25; 2,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,91</t>
+          <t>1,56; 4,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,19</t>
+          <t>0,25; 2,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,08</t>
+          <t>0,31; 3,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,22</t>
+          <t>0,55; 3,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,23; 3,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,39</t>
+          <t>0,65; 2,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,76</t>
+          <t>0,41; 1,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,28</t>
+          <t>0,55; 2,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,86</t>
+          <t>1,57; 3,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,04</t>
+          <t>0,34; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,71</t>
+          <t>1,06; 3,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,51</t>
+          <t>0,39; 2,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,04</t>
+          <t>1,73; 5,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,1</t>
+          <t>0,56; 4,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,07</t>
+          <t>0,79; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,33</t>
+          <t>1,91; 11,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,06</t>
+          <t>0,53; 2,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,44</t>
+          <t>1,24; 3,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,41</t>
+          <t>0,47; 2,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,19</t>
+          <t>2,22; 5,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,66</t>
+          <t>1,12; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,93</t>
+          <t>1,22; 3,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,04</t>
+          <t>0,47; 2,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,42</t>
+          <t>1,73; 3,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,52</t>
+          <t>0,73; 2,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,84</t>
+          <t>1,38; 3,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,05</t>
+          <t>0,59; 2,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 52,99</t>
+          <t>1,59; 3,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,43</t>
+          <t>1,15; 2,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,93</t>
+          <t>1,53; 2,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,68</t>
+          <t>0,65; 1,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 40,7</t>
+          <t>1,84; 3,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,71</t>
+          <t>1,26; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,28</t>
+          <t>0,4; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,99</t>
+          <t>0,68; 2,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,18</t>
+          <t>1,42; 4,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,52</t>
+          <t>0,53; 2,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,18</t>
+          <t>1,02; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,21</t>
+          <t>0,63; 2,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,38</t>
+          <t>3,56; 5,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,68</t>
+          <t>0,95; 2,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,4</t>
+          <t>0,91; 2,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,1</t>
+          <t>0,83; 2,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,77</t>
+          <t>3,05; 4,87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,19</t>
+          <t>0,7; 5,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,09</t>
+          <t>0,23; 4,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,98</t>
+          <t>1,34; 2,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,21</t>
+          <t>1,37; 3,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,73</t>
+          <t>0,42; 1,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,13</t>
+          <t>2,46; 4,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,6</t>
+          <t>1,16; 2,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,95</t>
+          <t>1,36; 2,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,56</t>
+          <t>0,45; 1,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,4</t>
+          <t>2,14; 4,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,05</t>
+          <t>1,19; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,24</t>
+          <t>1,27; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,44</t>
+          <t>0,71; 1,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,83</t>
+          <t>2,01; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,27; 2,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,67</t>
+          <t>1,65; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,48</t>
+          <t>0,76; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 25,99</t>
+          <t>2,69; 3,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,96</t>
+          <t>1,35; 1,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,29</t>
+          <t>1,57; 2,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,33</t>
+          <t>0,82; 1,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,52</t>
+          <t>2,5; 3,22</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>21825</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2612; 13836</t>
+          <t>2424; 13742</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3099; 16413</t>
+          <t>3035; 16205</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>782; 7050</t>
+          <t>783; 7197</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5728; 18517</t>
+          <t>5924; 19190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2914; 13333</t>
+          <t>2794; 12806</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4283; 18722</t>
+          <t>4567; 18613</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4650</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5468; 15340</t>
+          <t>6576; 16839</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7019; 21690</t>
+          <t>7052; 21218</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10266; 29286</t>
+          <t>9710; 29785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>895; 8045</t>
+          <t>903; 8956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13013; 28729</t>
+          <t>14313; 30385</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>22673</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2860; 13180</t>
+          <t>2818; 13534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>771; 7380</t>
+          <t>854; 8282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>949; 8354</t>
+          <t>952; 8435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6899; 22220</t>
+          <t>7545; 23804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>915; 8149</t>
+          <t>932; 8277</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1096; 10413</t>
+          <t>1055; 10479</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2024; 11996</t>
+          <t>2056; 12426</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4558; 14471</t>
+          <t>5186; 16798</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4988; 17641</t>
+          <t>4780; 16912</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2946; 13284</t>
+          <t>3076; 13909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4153; 17064</t>
+          <t>4131; 16154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13248; 32195</t>
+          <t>14267; 35285</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>22795</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1869; 11039</t>
+          <t>1868; 10505</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6316; 23334</t>
+          <t>6687; 22870</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2066; 13077</t>
+          <t>2028; 13858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3641; 26991</t>
+          <t>8181; 23711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>951; 8550</t>
+          <t>941; 7900</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2857; 13201</t>
+          <t>2043; 11816</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 10417</t>
+          <t>0; 14117</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3137; 17236</t>
+          <t>3582; 21034</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3217; 14624</t>
+          <t>3760; 16600</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11347; 30612</t>
+          <t>11005; 29437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3110; 16560</t>
+          <t>3213; 17077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7432; 35035</t>
+          <t>14619; 36404</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>222245</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>246141</t>
+          <t>48840</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13819; 32976</t>
+          <t>13908; 32003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14456; 33980</t>
+          <t>14170; 34829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6193; 23478</t>
+          <t>5388; 23194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15769; 35442</t>
+          <t>19535; 43338</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5229; 18006</t>
+          <t>5187; 18616</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11316; 29463</t>
+          <t>10586; 29487</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4764; 16900</t>
+          <t>4881; 17769</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18952; 518310</t>
+          <t>13662; 26425</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23270; 47372</t>
+          <t>22502; 44571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28486; 56428</t>
+          <t>29469; 56186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12447; 33177</t>
+          <t>12939; 32800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41542; 819284</t>
+          <t>36633; 66106</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34369</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>53739</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3779; 16501</t>
+          <t>4400; 16586</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2062; 11623</t>
+          <t>2038; 12352</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4546; 18590</t>
+          <t>4212; 18371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7917; 24612</t>
+          <t>8082; 23728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3165; 14353</t>
+          <t>3019; 13653</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8217; 24243</t>
+          <t>7749; 24171</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4607; 16326</t>
+          <t>4679; 17188</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23427; 45280</t>
+          <t>29617; 47817</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8656; 24679</t>
+          <t>8752; 24937</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12092; 30520</t>
+          <t>11609; 30507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10848; 28521</t>
+          <t>11336; 29328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37370; 62792</t>
+          <t>42695; 68074</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>32665</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8749</t>
+          <t>0; 8392</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1924; 13849</t>
+          <t>1875; 13650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5826</t>
+          <t>0; 6702</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>296; 5023</t>
+          <t>537; 11211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16248; 37256</t>
+          <t>16742; 36577</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15238; 35612</t>
+          <t>15219; 34761</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4846; 18710</t>
+          <t>4596; 18170</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17319; 31459</t>
+          <t>20811; 40322</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18574; 40164</t>
+          <t>17982; 39101</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18741; 40648</t>
+          <t>18770; 40231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6119; 21387</t>
+          <t>6220; 19918</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18662; 34062</t>
+          <t>23191; 45273</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>86703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>304753</t>
+          <t>115833</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>380175</t>
+          <t>202537</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37639; 67095</t>
+          <t>38793; 65808</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43631; 76591</t>
+          <t>43411; 75514</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23001; 48689</t>
+          <t>24151; 49838</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56748; 95418</t>
+          <t>69300; 109197</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>42920; 74087</t>
+          <t>42996; 72290</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59959; 94752</t>
+          <t>58433; 94656</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26445; 52401</t>
+          <t>26971; 53624</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100983; 929866</t>
+          <t>97927; 135229</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>87079; 130229</t>
+          <t>89680; 130570</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112766; 159654</t>
+          <t>109470; 159167</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55780; 91935</t>
+          <t>57049; 92008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>172038; 1079339</t>
+          <t>176806; 227882</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
